--- a/StructureDefinition-tk-endpoint-security-method.xlsx
+++ b/StructureDefinition-tk-endpoint-security-method.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:34:42+00:00</t>
+    <t>2026-09-08T11:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-endpoint-security-method.xlsx
+++ b/StructureDefinition-tk-endpoint-security-method.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:28:32+00:00</t>
+    <t>2026-09-08T11:37:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-endpoint-security-method.xlsx
+++ b/StructureDefinition-tk-endpoint-security-method.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:37:33+00:00</t>
+    <t>2026-09-08T12:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-endpoint-security-method.xlsx
+++ b/StructureDefinition-tk-endpoint-security-method.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:25:30+00:00</t>
+    <t>2026-09-09T11:47:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-endpoint-security-method.xlsx
+++ b/StructureDefinition-tk-endpoint-security-method.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:47:00+00:00</t>
+    <t>2026-09-10T06:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-endpoint-security-method.xlsx
+++ b/StructureDefinition-tk-endpoint-security-method.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T06:56:47+00:00</t>
+    <t>2026-09-10T07:38:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
